--- a/samples/generated/piu_full_build.xlsx
+++ b/samples/generated/piu_full_build.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr"/>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr"/>
@@ -3464,53 +3464,45 @@
       <c r="J91" s="9" t="inlineStr"/>
       <c r="K91" s="9" t="inlineStr"/>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Radio Speaker</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>CENTER CONSOLE &amp; COMPUTER</t>
         </is>
       </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="7" t="n"/>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Center Console</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>GAMBER JOHNSON</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>VEHICLE SPECIFIC</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="7" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="9" t="n"/>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Special Face Plate 1</t>
+          <t>Center Console</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -3530,7 +3522,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>CORE CONTROL HEAD</t>
+          <t>VEHICLE SPECIFIC</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr"/>
@@ -3545,7 +3537,7 @@
       <c r="A95" s="7" t="n"/>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>Special Face Plate 2</t>
+          <t>Special Face Plate 1</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3580,7 +3572,7 @@
       <c r="A96" s="9" t="n"/>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Special Face Plate 3</t>
+          <t>Special Face Plate 2</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -3615,7 +3607,7 @@
       <c r="A97" s="7" t="n"/>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>Special Face Plate 4</t>
+          <t>Special Face Plate 3</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -3650,7 +3642,7 @@
       <c r="A98" s="9" t="n"/>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Special Face Plate 5</t>
+          <t>Special Face Plate 4</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -3685,7 +3677,7 @@
       <c r="A99" s="7" t="n"/>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>Special Face Plate 6</t>
+          <t>Special Face Plate 5</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -3720,7 +3712,7 @@
       <c r="A100" s="9" t="n"/>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Special Face Plate 7</t>
+          <t>Special Face Plate 6</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
@@ -3755,7 +3747,7 @@
       <c r="A101" s="7" t="n"/>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>Arm Rest</t>
+          <t>Special Face Plate 7</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -3775,7 +3767,7 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>STANDARD ARM REST</t>
+          <t>CORE CONTROL HEAD</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr"/>
@@ -3790,7 +3782,7 @@
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Motion Attachment</t>
+          <t>Arm Rest</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -3810,14 +3802,10 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>9"" MONGOOSE</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>MOUNTED TO CONSOLE</t>
-        </is>
-      </c>
+          <t>STANDARD ARM REST</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="inlineStr"/>
       <c r="I102" s="9" t="n">
         <v>1</v>
@@ -3829,7 +3817,7 @@
       <c r="A103" s="7" t="n"/>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Docking Station</t>
+          <t>Motion Attachment</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
@@ -3849,10 +3837,14 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY DOCK</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr"/>
+          <t>9"" MONGOOSE</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>MOUNTED TO CONSOLE</t>
+        </is>
+      </c>
       <c r="H103" s="7" t="inlineStr"/>
       <c r="I103" s="7" t="n">
         <v>1</v>
@@ -3860,57 +3852,53 @@
       <c r="J103" s="7" t="inlineStr"/>
       <c r="K103" s="7" t="inlineStr"/>
     </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Docking Station</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>GAMBER JOHNSON</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY DOCK</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>PRINTER</t>
         </is>
       </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="9" t="n"/>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>Printer</t>
-        </is>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>BROTHER</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>PJ-822</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>PRINTER ARMREST MOUNT</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="inlineStr"/>
-      <c r="I105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="9" t="inlineStr"/>
-      <c r="K105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="7" t="n"/>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>Printer Mount</t>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Printer</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -3925,15 +3913,19 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>GAMBER JOHNSON</t>
+          <t>BROTHER</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY MODEL</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr"/>
+          <t>PJ-822</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>PRINTER ARMREST MOUNT</t>
+        </is>
+      </c>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="n">
         <v>1</v>
@@ -3945,7 +3937,7 @@
       <c r="A107" s="9" t="n"/>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Printer Power</t>
+          <t>Printer Mount</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -3958,8 +3950,16 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E107" s="9" t="inlineStr"/>
-      <c r="F107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>GAMBER JOHNSON</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY MODEL</t>
+        </is>
+      </c>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="n">
@@ -3972,7 +3972,7 @@
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>Printer USB</t>
+          <t>Printer Power</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -3997,9 +3997,9 @@
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="9" t="n"/>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>12v Aux Ports</t>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Printer USB</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -4012,81 +4012,69 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>SHO-ME</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>USB TYPE A</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>RIGHT SIDE ON CONSOLE</t>
-        </is>
-      </c>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I109" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="J109" s="9" t="inlineStr"/>
       <c r="K109" s="9" t="inlineStr"/>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>12v Aux Ports</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>SHO-ME</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>USB TYPE A</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>RIGHT SIDE ON CONSOLE</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr"/>
+      <c r="K110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>CAMERAS &amp; DVR</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="7" t="n"/>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Camera DVR</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>AXON</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>FLEET 3</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>ON FRONT PARTITION</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr"/>
-      <c r="I111" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="7" t="inlineStr"/>
-      <c r="K111" s="7" t="inlineStr"/>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="9" t="n"/>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Front Camera</t>
+          <t>Camera DVR</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -4099,9 +4087,21 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr"/>
-      <c r="F112" s="9" t="inlineStr"/>
-      <c r="G112" s="9" t="inlineStr"/>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>AXON</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>FLEET 3</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>ON FRONT PARTITION</t>
+        </is>
+      </c>
       <c r="H112" s="9" t="inlineStr"/>
       <c r="I112" s="9" t="n">
         <v>1</v>
@@ -4111,9 +4111,9 @@
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="7" t="n"/>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>Body Camera Dock</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Front Camera</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -4128,11 +4128,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>PASSENGER SIDE VISOR</t>
-        </is>
-      </c>
+      <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="n">
         <v>1</v>
@@ -4144,7 +4140,7 @@
       <c r="A114" s="9" t="n"/>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Rear Seat Camera</t>
+          <t>Body Camera Dock</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
@@ -4161,7 +4157,7 @@
       <c r="F114" s="9" t="inlineStr"/>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>ON DRIVER SIDE HEADLINER</t>
+          <t>PASSENGER SIDE VISOR</t>
         </is>
       </c>
       <c r="H114" s="9" t="inlineStr"/>
@@ -4173,9 +4169,9 @@
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="7" t="n"/>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>Rear Camera</t>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Rear Seat Camera</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
@@ -4190,7 +4186,11 @@
       </c>
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>ON DRIVER SIDE HEADLINER</t>
+        </is>
+      </c>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="7" t="n">
         <v>1</v>
@@ -4202,7 +4202,7 @@
       <c r="A116" s="9" t="n"/>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Wireless Mic Charger</t>
+          <t>Rear Camera</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -4217,11 +4217,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr"/>
       <c r="F116" s="9" t="inlineStr"/>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>PASSENGER SIDE VISOR</t>
-        </is>
-      </c>
+      <c r="G116" s="9" t="inlineStr"/>
       <c r="H116" s="9" t="inlineStr"/>
       <c r="I116" s="9" t="n">
         <v>1</v>
@@ -4229,53 +4225,49 @@
       <c r="J116" s="9" t="inlineStr"/>
       <c r="K116" s="9" t="inlineStr"/>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Wireless Mic Charger</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr"/>
+      <c r="F117" s="7" t="inlineStr"/>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>PASSENGER SIDE VISOR</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="7" t="inlineStr"/>
+      <c r="K117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>PARTITIONS &amp; PRISONER AREA</t>
         </is>
       </c>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="7" t="n"/>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Front Partition</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>FULL PARTITION</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr"/>
-      <c r="I118" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="7" t="inlineStr"/>
-      <c r="K118" s="7" t="inlineStr"/>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="9" t="n"/>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>Chicago Barrier</t>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Front Partition</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -4288,10 +4280,14 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E119" s="9" t="inlineStr"/>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>STEEL</t>
+          <t>FULL PARTITION</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr"/>
@@ -4306,7 +4302,7 @@
       <c r="A120" s="7" t="n"/>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Front Partition Transfer Kit</t>
+          <t>Chicago Barrier</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -4320,7 +4316,11 @@
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr"/>
-      <c r="F120" s="7" t="inlineStr"/>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>STEEL</t>
+        </is>
+      </c>
       <c r="G120" s="7" t="inlineStr"/>
       <c r="H120" s="7" t="inlineStr"/>
       <c r="I120" s="7" t="n">
@@ -4331,9 +4331,9 @@
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="9" t="n"/>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>Rear Seat Lights 1</t>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Front Partition Transfer Kit</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
@@ -4346,43 +4346,21 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>LOWER KICK PANEL(S)</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
+      <c r="E121" s="9" t="inlineStr"/>
+      <c r="F121" s="9" t="inlineStr"/>
+      <c r="G121" s="9" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
+      <c r="I121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="9" t="inlineStr"/>
       <c r="K121" s="9" t="inlineStr"/>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="7" t="n"/>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Rear Seat Lights 2</t>
+          <t>Rear Seat Lights 1</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
@@ -4422,7 +4400,7 @@
       </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr"/>
@@ -4431,7 +4409,7 @@
       <c r="A123" s="9" t="n"/>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Rear Seat Cargo Lights</t>
+          <t>Rear Seat Lights 2</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -4456,7 +4434,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>HEADLINER</t>
+          <t>LOWER KICK PANEL(S)</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -4471,7 +4449,7 @@
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>STANDARD LENSE</t>
+          <t>STANDARD LENS</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr"/>
@@ -4480,7 +4458,7 @@
       <c r="A124" s="7" t="n"/>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Rear Seat Divider</t>
+          <t>Rear Seat Cargo Lights</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -4495,27 +4473,41 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>SETINA</t>
+          <t>WHELEN</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>POLY DIVIDER</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="7" t="inlineStr"/>
-      <c r="I124" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="7" t="inlineStr"/>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>HEADLINER</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
       <c r="K124" s="7" t="inlineStr"/>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="9" t="n"/>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Rear Window Bars</t>
+          <t>Rear Seat Divider</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -4535,7 +4527,7 @@
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>STEEL VERTICAL</t>
+          <t>POLY DIVIDER</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr"/>
@@ -4550,7 +4542,7 @@
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Replacement Rear Seat</t>
+          <t>Rear Window Bars</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -4570,7 +4562,7 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>FULL REPLACMENT SEAT W/ CENTER PULL SEAT BELTS</t>
+          <t>STEEL VERTICAL</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr"/>
@@ -4585,7 +4577,7 @@
       <c r="A127" s="9" t="n"/>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Rear Partition</t>
+          <t>Replacement Rear Seat</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -4605,7 +4597,7 @@
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>STEEL WINDOW</t>
+          <t>FULL REPLACMENT SEAT W/ CENTER PULL SEAT BELTS</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr"/>
@@ -4620,7 +4612,7 @@
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Floor Pan</t>
+          <t>Rear Partition</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
@@ -4640,7 +4632,7 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>POLY FLOOR PAN</t>
+          <t>STEEL WINDOW</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr"/>
@@ -4651,57 +4643,53 @@
       <c r="J128" s="7" t="inlineStr"/>
       <c r="K128" s="7" t="inlineStr"/>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
+    <row r="129" ht="15" customHeight="1">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Floor Pan</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>POLY FLOOR PAN</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
+      <c r="I129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="9" t="inlineStr"/>
+      <c r="K129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>ARMOR &amp; PROTECTION</t>
         </is>
       </c>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="9" t="n"/>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t>Bullet Proof Door Panel(s)</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D130" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E130" s="9" t="inlineStr">
-        <is>
-          <t>ANGEL ARMOR</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>LEVEL 3A (HANDGUN)</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>DRIVERS DOOR ONLY</t>
-        </is>
-      </c>
-      <c r="H130" s="9" t="inlineStr"/>
-      <c r="I130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="9" t="inlineStr"/>
-      <c r="K130" s="9" t="inlineStr"/>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="7" t="n"/>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>Bullet Proof Door Window(s)</t>
+          <t>Bullet Proof Door Panel(s)</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -4716,7 +4704,7 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>SPECIFY MFG</t>
+          <t>ANGEL ARMOR</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -4736,49 +4724,57 @@
       <c r="J131" s="7" t="inlineStr"/>
       <c r="K131" s="7" t="inlineStr"/>
     </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>Bullet Proof Door Window(s)</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>SPECIFY MFG</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>LEVEL 3A (HANDGUN)</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>DRIVERS DOOR ONLY</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr"/>
+      <c r="I132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="9" t="inlineStr"/>
+      <c r="K132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>CARGO &amp; STORAGE</t>
         </is>
       </c>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="9" t="n"/>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>Storage Compartment</t>
-        </is>
-      </c>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E133" s="9" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="inlineStr"/>
-      <c r="G133" s="9" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
-      <c r="I133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="9" t="inlineStr"/>
-      <c r="K133" s="9" t="inlineStr"/>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="7" t="n"/>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Cargo Lighting</t>
+          <t>Storage Compartment</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -4793,41 +4789,23 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>3"" ROUND</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>ON LIFT GATE</t>
-        </is>
-      </c>
-      <c r="H134" s="7" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" s="7" t="inlineStr">
-        <is>
-          <t>STANDARD LENSE</t>
-        </is>
-      </c>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr"/>
+      <c r="G134" s="7" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr"/>
+      <c r="I134" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="7" t="inlineStr"/>
       <c r="K134" s="7" t="inlineStr"/>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="9" t="n"/>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Door Lock Button</t>
+          <t>Cargo Lighting</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -4840,25 +4818,43 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr"/>
-      <c r="F135" s="9" t="inlineStr"/>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>WHELEN</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>3"" ROUND</t>
+        </is>
+      </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>ON LEFT D-PILLAR</t>
-        </is>
-      </c>
-      <c r="H135" s="9" t="inlineStr"/>
-      <c r="I135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" s="9" t="inlineStr"/>
+          <t>ON LIFT GATE</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>STANDARD LENS</t>
+        </is>
+      </c>
       <c r="K135" s="9" t="inlineStr"/>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="7" t="n"/>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Equipment Tray</t>
+          <t>Door Lock Button</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -4871,19 +4867,11 @@
           <t>DTM</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>EQUIPMENT DRAWER</t>
-        </is>
-      </c>
+      <c r="E136" s="7" t="inlineStr"/>
+      <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>ON REAR PARTITION</t>
+          <t>ON LEFT D-PILLAR</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr"/>
@@ -4893,57 +4881,57 @@
       <c r="J136" s="7" t="inlineStr"/>
       <c r="K136" s="7" t="inlineStr"/>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Equipment Tray</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>EQUIPMENT DRAWER</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>ON REAR PARTITION</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr"/>
+      <c r="I137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="9" t="inlineStr"/>
+      <c r="K137" s="9" t="inlineStr"/>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>GUNLOCKS</t>
         </is>
       </c>
-    </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="9" t="n"/>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t>Gunlock 1</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>SANTA CRUZ</t>
-        </is>
-      </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G138" s="9" t="inlineStr">
-        <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
-        </is>
-      </c>
-      <c r="H138" s="9" t="inlineStr"/>
-      <c r="I138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="9" t="inlineStr"/>
-      <c r="K138" s="9" t="inlineStr"/>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="7" t="n"/>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>Gunlock Bracket 1</t>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 1</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -4958,15 +4946,19 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>SETINA</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>FRONT OVERHEAD BRACKETS</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr"/>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEAD ON FRONT PARTITION</t>
+        </is>
+      </c>
       <c r="H139" s="7" t="inlineStr"/>
       <c r="I139" s="7" t="n">
         <v>1</v>
@@ -4976,9 +4968,9 @@
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="9" t="n"/>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t>Gunlock 2</t>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Gunlock Bracket 1</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
@@ -4993,19 +4985,15 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>SETINA</t>
         </is>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
-        </is>
-      </c>
+          <t>FRONT OVERHEAD BRACKETS</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr"/>
       <c r="H140" s="9" t="inlineStr"/>
       <c r="I140" s="9" t="n">
         <v>1</v>
@@ -5015,9 +5003,9 @@
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="7" t="n"/>
-      <c r="B141" s="12" t="inlineStr">
-        <is>
-          <t>Gunlock Bracket 2</t>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 2</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -5032,15 +5020,19 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>SETINA</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>FRONT OVERHEAD BRACKETS</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr"/>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEAD ON FRONT PARTITION</t>
+        </is>
+      </c>
       <c r="H141" s="7" t="inlineStr"/>
       <c r="I141" s="7" t="n">
         <v>1</v>
@@ -5050,9 +5042,9 @@
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="9" t="n"/>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t>Gunlock 3</t>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Gunlock Bracket 2</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
@@ -5067,19 +5059,15 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>SETINA</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>SINGLE HANDCUFF</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>OVERHEAD ON FRONT PARTITION</t>
-        </is>
-      </c>
+          <t>FRONT OVERHEAD BRACKETS</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr"/>
       <c r="H142" s="9" t="inlineStr"/>
       <c r="I142" s="9" t="n">
         <v>1</v>
@@ -5089,9 +5077,9 @@
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="7" t="n"/>
-      <c r="B143" s="12" t="inlineStr">
-        <is>
-          <t>Gunlock Bracket 3</t>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Gunlock 3</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -5106,15 +5094,19 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>SETINA</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>FRONT OVERHEAD BRACKETS</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr"/>
+          <t>SINGLE HANDCUFF</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>OVERHEAD ON FRONT PARTITION</t>
+        </is>
+      </c>
       <c r="H143" s="7" t="inlineStr"/>
       <c r="I143" s="7" t="n">
         <v>1</v>
@@ -5122,53 +5114,53 @@
       <c r="J143" s="7" t="inlineStr"/>
       <c r="K143" s="7" t="inlineStr"/>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Gunlock Bracket 3</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>SETINA</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>FRONT OVERHEAD BRACKETS</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr"/>
+      <c r="I144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="9" t="inlineStr"/>
+      <c r="K144" s="9" t="inlineStr"/>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>K-9 EQUIPMENT</t>
         </is>
       </c>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="9" t="n"/>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>K-9 Kennel</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D145" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E145" s="9" t="inlineStr">
-        <is>
-          <t>SETINA</t>
-        </is>
-      </c>
-      <c r="F145" s="9" t="inlineStr">
-        <is>
-          <t>FULL PLATFORM</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr"/>
-      <c r="I145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="9" t="inlineStr"/>
-      <c r="K145" s="9" t="inlineStr"/>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="7" t="n"/>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>K-9 Heat Alarm/Popper</t>
+          <t>K-9 Kennel</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
@@ -5183,19 +5175,15 @@
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>ACE K-9</t>
+          <t>SETINA</t>
         </is>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>HEAT ALARM ONLY</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>ON FRONT OF K-9 PARTITION</t>
-        </is>
-      </c>
+          <t>FULL PLATFORM</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr"/>
       <c r="H146" s="7" t="inlineStr"/>
       <c r="I146" s="7" t="n">
         <v>1</v>
@@ -5207,7 +5195,7 @@
       <c r="A147" s="9" t="n"/>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>K-9 Control Head</t>
+          <t>K-9 Heat Alarm/Popper</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
@@ -5225,10 +5213,14 @@
           <t>ACE K-9</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr"/>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>HEAT ALARM ONLY</t>
+        </is>
+      </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>IN CENTER CONSOLE</t>
+          <t>ON FRONT OF K-9 PARTITION</t>
         </is>
       </c>
       <c r="H147" s="9" t="inlineStr"/>
@@ -5242,7 +5234,7 @@
       <c r="A148" s="7" t="n"/>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>K-9 Add-Ons</t>
+          <t>K-9 Control Head</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
@@ -5273,53 +5265,53 @@
       <c r="J148" s="7" t="inlineStr"/>
       <c r="K148" s="7" t="inlineStr"/>
     </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" s="9" t="n"/>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>K-9 Add-Ons</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>ACE K-9</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr"/>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>IN CENTER CONSOLE</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr"/>
+      <c r="I149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="9" t="inlineStr"/>
+      <c r="K149" s="9" t="inlineStr"/>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>ELECTRICAL &amp; POWER</t>
         </is>
       </c>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="9" t="n"/>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>Battery Tender</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>SCHUMACHER</t>
-        </is>
-      </c>
-      <c r="F150" s="9" t="inlineStr"/>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>ON EQUIPMENT TRAY</t>
-        </is>
-      </c>
-      <c r="H150" s="9" t="inlineStr"/>
-      <c r="I150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="9" t="inlineStr"/>
-      <c r="K150" s="9" t="inlineStr"/>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="7" t="n"/>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>Auto Eject</t>
+          <t>Battery Tender</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
@@ -5334,17 +5326,13 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>KUSSMAUL</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>WATER PROOF</t>
-        </is>
-      </c>
+          <t>SCHUMACHER</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr"/>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>LEFT FRONT QUARTER PANEL</t>
+          <t>ON EQUIPMENT TRAY</t>
         </is>
       </c>
       <c r="H151" s="7" t="inlineStr"/>
@@ -5354,53 +5342,57 @@
       <c r="J151" s="7" t="inlineStr"/>
       <c r="K151" s="7" t="inlineStr"/>
     </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Auto Eject</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>KUSSMAUL</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>WATER PROOF</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>LEFT FRONT QUARTER PANEL</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr"/>
+      <c r="I152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="9" t="inlineStr"/>
+      <c r="K152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>CONNECTED SYSTEMS</t>
         </is>
       </c>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="9" t="n"/>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>Vehicle to Vehicle Sync</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr"/>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>IN LIGHT BAR</t>
-        </is>
-      </c>
-      <c r="H153" s="9" t="inlineStr"/>
-      <c r="I153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="9" t="inlineStr"/>
-      <c r="K153" s="9" t="inlineStr"/>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" s="7" t="n"/>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Cloud System</t>
+          <t>Vehicle to Vehicle Sync</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
@@ -5418,14 +5410,10 @@
           <t>WHELEN</t>
         </is>
       </c>
-      <c r="F154" s="7" t="inlineStr">
-        <is>
-          <t>VERIZON ROOF MOUNT</t>
-        </is>
-      </c>
+      <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>ON EQUIPMENT TRAY</t>
+          <t>IN LIGHT BAR</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr"/>
@@ -5439,7 +5427,7 @@
       <c r="A155" s="9" t="n"/>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Remote Start</t>
+          <t>Cloud System</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -5454,15 +5442,19 @@
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>ARCTI START</t>
+          <t>WHELEN</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>1 BUTTON 1 WAY</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr"/>
+          <t>VERIZON ROOF MOUNT</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>ON EQUIPMENT TRAY</t>
+        </is>
+      </c>
       <c r="H155" s="9" t="inlineStr"/>
       <c r="I155" s="9" t="n">
         <v>1</v>
@@ -5470,59 +5462,53 @@
       <c r="J155" s="9" t="inlineStr"/>
       <c r="K155" s="9" t="inlineStr"/>
     </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="7" t="n"/>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Remote Start</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>ARCTI START</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>1 BUTTON 1 WAY</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr"/>
+      <c r="H156" s="7" t="inlineStr"/>
+      <c r="I156" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="7" t="inlineStr"/>
+      <c r="K156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>ARGES &amp; SPOTLIGHT</t>
         </is>
       </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="7" t="n"/>
-      <c r="B157" s="8" t="inlineStr">
-        <is>
-          <t>Arges</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>WHELEN</t>
-        </is>
-      </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>PRO-FOCUS</t>
-        </is>
-      </c>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>LEFT FRONT FENDER</t>
-        </is>
-      </c>
-      <c r="H157" s="7" t="inlineStr"/>
-      <c r="I157" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" s="7" t="inlineStr"/>
-      <c r="K157" s="7" t="inlineStr"/>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="9" t="n"/>
-      <c r="B158" s="11" t="inlineStr">
-        <is>
-          <t>Arges Controller</t>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>Arges</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
@@ -5542,17 +5528,19 @@
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>ARGES W/ BAIL BRACKET</t>
+          <t>PRO-FOCUS</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>LEFT ON DASH</t>
+          <t>LEFT FRONT FENDER</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr"/>
-      <c r="I158" s="9" t="n">
-        <v>1</v>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J158" s="9" t="inlineStr"/>
       <c r="K158" s="9" t="inlineStr"/>
@@ -5561,7 +5549,7 @@
       <c r="A159" s="7" t="n"/>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>Arges Mount</t>
+          <t>Arges Controller</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
@@ -5581,10 +5569,14 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>VEHICLE SPECIFIC MOUNT</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr"/>
+          <t>ARGES W/ BAIL BRACKET</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>LEFT ON DASH</t>
+        </is>
+      </c>
       <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="n">
         <v>1</v>
@@ -5594,9 +5586,9 @@
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" s="9" t="n"/>
-      <c r="B160" s="10" t="inlineStr">
-        <is>
-          <t>Photo Eye</t>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>Arges Mount</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
@@ -5616,7 +5608,7 @@
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>CENTER OF DASH</t>
+          <t>VEHICLE SPECIFIC MOUNT</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr"/>
@@ -5631,7 +5623,7 @@
       <c r="A161" s="7" t="n"/>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>GPD W/ Extension</t>
+          <t>Photo Eye</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
@@ -5646,7 +5638,7 @@
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>GLOBESAT</t>
+          <t>WHELEN</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -5662,57 +5654,53 @@
       <c r="J161" s="7" t="inlineStr"/>
       <c r="K161" s="7" t="inlineStr"/>
     </row>
-    <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>GPD W/ Extension</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>GLOBESAT</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>CENTER OF DASH</t>
+        </is>
+      </c>
+      <c r="G162" s="9" t="inlineStr"/>
+      <c r="H162" s="9" t="inlineStr"/>
+      <c r="I162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="9" t="inlineStr"/>
+      <c r="K162" s="9" t="inlineStr"/>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>FINISHING &amp; ACCESSORIES</t>
         </is>
       </c>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>Floor Mats</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>DTM</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>WEATHER TECH</t>
-        </is>
-      </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>SPECIFY MODEL</t>
-        </is>
-      </c>
-      <c r="G163" s="9" t="inlineStr">
-        <is>
-          <t>FRONT DRIVER AND PASSENGER</t>
-        </is>
-      </c>
-      <c r="H163" s="9" t="inlineStr"/>
-      <c r="I163" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="9" t="inlineStr"/>
-      <c r="K163" s="9" t="inlineStr"/>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="7" t="n"/>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Seat Covers</t>
+          <t>Floor Mats</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
@@ -5727,24 +5715,20 @@
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>TIGER TOUGH</t>
+          <t>WEATHER TECH</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>SPECIFY MODEL</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>DRIVER ONLY</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
+          <t>FRONT DRIVER AND PASSENGER</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr"/>
       <c r="I164" s="7" t="n">
         <v>1</v>
       </c>
@@ -5755,7 +5739,7 @@
       <c r="A165" s="9" t="n"/>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Window Tint</t>
+          <t>Seat Covers</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -5770,16 +5754,24 @@
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>5-0 FAB (DTM)</t>
+          <t>TIGER TOUGH</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>COMPLETE SQUAD HARNESS</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr"/>
-      <c r="H165" s="9" t="inlineStr"/>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>DRIVER ONLY</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
       <c r="I165" s="9" t="n">
         <v>1</v>
       </c>
@@ -5790,7 +5782,7 @@
       <c r="A166" s="7" t="n"/>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Decals</t>
+          <t>Window Tint</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
@@ -5805,12 +5797,12 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>ADVANCED GRAPHICS</t>
+          <t>5-0 FAB (DTM)</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>CUSTOM GRAPHICS ( WORK WITH MFG)</t>
+          <t>COMPLETE SQUAD HARNESS</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr"/>
@@ -5825,7 +5817,7 @@
       <c r="A167" s="9" t="n"/>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>Decals</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -5840,12 +5832,12 @@
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>5-0 FAB (DTM)</t>
+          <t>ADVANCED GRAPHICS</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>COMPLETE SQUAD HARNESS</t>
+          <t>CUSTOM GRAPHICS ( WORK WITH MFG)</t>
         </is>
       </c>
       <c r="G167" s="9" t="inlineStr"/>
@@ -5856,10 +5848,45 @@
       <c r="J167" s="9" t="inlineStr"/>
       <c r="K167" s="9" t="inlineStr"/>
     </row>
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="7" t="n"/>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Harness</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>DTM</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>5-0 FAB (DTM)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>COMPLETE SQUAD HARNESS</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr"/>
+      <c r="I168" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="7" t="inlineStr"/>
+      <c r="K168" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="57">
     <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A130:K130"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="H3:K3"/>
@@ -5869,37 +5896,38 @@
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="A77:K77"/>
     <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A157:K157"/>
+    <mergeCell ref="A138:K138"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A70:K70"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A110:K110"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A132:K132"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="G7:K7"/>
-    <mergeCell ref="A162:K162"/>
+    <mergeCell ref="A153:K153"/>
     <mergeCell ref="H8:K8"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A137:K137"/>
+    <mergeCell ref="A133:K133"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A118:K118"/>
     <mergeCell ref="H10:K10"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="H4:K4"/>
-    <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A163:K163"/>
     <mergeCell ref="H9:K9"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A104:K104"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A129:K129"/>
     <mergeCell ref="A85:K85"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A150:K150"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="A20:K20"/>
@@ -5909,12 +5937,11 @@
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A152:K152"/>
-    <mergeCell ref="A117:K117"/>
-    <mergeCell ref="A156:K156"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A93:K93"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A111:K111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
